--- a/cet4/result/67_乡村女神_振兴之路的传奇/67_乡村女神_振兴之路的传奇_学习版.xlsx
+++ b/cet4/result/67_乡村女神_振兴之路的传奇/67_乡村女神_振兴之路的传奇_学习版.xlsx
@@ -397,731 +397,633 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D44"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>village</v>
       </c>
       <c r="B2" t="str">
-        <v>village</v>
+        <v>/ˈvɪlɪdʒ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>村庄</v>
       </c>
-      <c r="D2" t="str">
-        <v>village(村庄)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>rural</v>
       </c>
       <c r="B3" t="str">
-        <v>rural</v>
+        <v>/ˈrʊrəl/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>乡村</v>
       </c>
-      <c r="D3" t="str">
-        <v>rural(乡村)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>warmth</v>
       </c>
       <c r="B4" t="str">
-        <v>warmth</v>
+        <v>/wɔːrmθ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>温暖</v>
       </c>
-      <c r="D4" t="str">
-        <v>warmth(温暖)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>Friday</v>
       </c>
       <c r="B5" t="str">
-        <v>Friday</v>
+        <v>/ˈfraɪdeɪ,ˈfraɪdi/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>星期五</v>
       </c>
-      <c r="D5" t="str">
-        <v>Friday(星期五)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>mild</v>
       </c>
       <c r="B6" t="str">
-        <v>mild</v>
+        <v>/maɪld/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>温和</v>
       </c>
-      <c r="D6" t="str">
-        <v>mild(温和)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>February</v>
       </c>
       <c r="B7" t="str">
-        <v>February</v>
+        <v>/ˈfebrueri/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>二月</v>
       </c>
-      <c r="D7" t="str">
-        <v>February(二月)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>name</v>
       </c>
       <c r="B8" t="str">
-        <v>name</v>
+        <v>/neɪm/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>名字</v>
       </c>
-      <c r="D8" t="str">
-        <v>name(名字)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>invitation</v>
       </c>
       <c r="B9" t="str">
-        <v>invitation</v>
+        <v>/ˌɪnvɪˈteɪʃn/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>邀请函</v>
       </c>
-      <c r="D9" t="str">
-        <v>invitation(邀请函)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>necessity</v>
       </c>
       <c r="B10" t="str">
-        <v>necessity</v>
+        <v>/nəˈsesəti/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>必需</v>
       </c>
-      <c r="D10" t="str">
-        <v>necessity(必需)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>would</v>
       </c>
       <c r="B11" t="str">
-        <v>would</v>
+        <v>/wʊd,wəd,əd/</v>
       </c>
       <c r="C11" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D11" t="str">
         <v>愿意</v>
       </c>
-      <c r="D11" t="str">
-        <v>would(愿意)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>brick</v>
       </c>
       <c r="B12" t="str">
-        <v>brick</v>
+        <v>/brɪk/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>砖</v>
       </c>
-      <c r="D12" t="str">
-        <v>brick(砖)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>rather</v>
       </c>
       <c r="B13" t="str">
-        <v>rather</v>
+        <v>/ˈræðər/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./v./adv./conj./int.</v>
+      </c>
+      <c r="D13" t="str">
         <v>宁愿</v>
       </c>
-      <c r="D13" t="str">
-        <v>rather(宁愿)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>communicate</v>
       </c>
       <c r="B14" t="str">
-        <v>communicate</v>
+        <v>/kəˈmjuːnɪkeɪt/</v>
       </c>
       <c r="C14" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>交流</v>
       </c>
-      <c r="D14" t="str">
-        <v>communicate(交流)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>approximately</v>
       </c>
       <c r="B15" t="str">
-        <v>approximately</v>
+        <v>/əˈprɑːksɪmətli/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D15" t="str">
         <v>大约</v>
       </c>
-      <c r="D15" t="str">
-        <v>approximately(大约)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>employer</v>
       </c>
       <c r="B16" t="str">
-        <v>employer</v>
+        <v>/ɪmˈplɔɪər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>雇主</v>
       </c>
-      <c r="D16" t="str">
-        <v>employer(雇主)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>much</v>
       </c>
       <c r="B17" t="str">
-        <v>much</v>
+        <v>/mʌtʃ/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v./adj./adv./pron.</v>
+      </c>
+      <c r="D17" t="str">
         <v>许多</v>
       </c>
-      <c r="D17" t="str">
-        <v>much(许多)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>castle</v>
       </c>
       <c r="B18" t="str">
-        <v>castle</v>
+        <v>/ˈkæsl/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>城堡</v>
       </c>
-      <c r="D18" t="str">
-        <v>castle(城堡)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>handle</v>
       </c>
       <c r="B19" t="str">
-        <v>handle</v>
+        <v>/ˈhændl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D19" t="str">
         <v>处理</v>
       </c>
-      <c r="D19" t="str">
-        <v>handle(处理)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>disagree</v>
       </c>
       <c r="B20" t="str">
-        <v>disagree</v>
+        <v>/ˌdɪsəˈɡriː/</v>
       </c>
       <c r="C20" t="str">
+        <v>vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>不同意</v>
       </c>
-      <c r="D20" t="str">
-        <v>disagree(不同意)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>disturb</v>
       </c>
       <c r="B21" t="str">
-        <v>disturb</v>
+        <v>/dɪˈstɜːrb/</v>
       </c>
       <c r="C21" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D21" t="str">
         <v>打扰</v>
       </c>
-      <c r="D21" t="str">
-        <v>disturb(打扰)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>Swiss</v>
       </c>
       <c r="B22" t="str">
-        <v>Swiss</v>
+        <v>/swɪs/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>瑞士</v>
       </c>
-      <c r="D22" t="str">
-        <v>Swiss(瑞士)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>Portuguese</v>
       </c>
       <c r="B23" t="str">
-        <v>Portuguese</v>
+        <v>/ˌpɔːrtʃuˈɡiːz/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>葡萄牙</v>
       </c>
-      <c r="D23" t="str">
-        <v>Portuguese(葡萄牙)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>soft</v>
       </c>
       <c r="B24" t="str">
-        <v>soft</v>
+        <v>/sɔːft/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>软件</v>
       </c>
-      <c r="D24" t="str">
-        <v>soft(软件)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>train</v>
       </c>
       <c r="B25" t="str">
-        <v>train</v>
+        <v>/treɪn/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D25" t="str">
         <v>火车</v>
       </c>
-      <c r="D25" t="str">
-        <v>train(火车)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>Sunday</v>
       </c>
       <c r="B26" t="str">
-        <v>rather</v>
+        <v>/'sʌndi/</v>
       </c>
       <c r="C26" t="str">
-        <v>相当</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>rather(相当)📢</v>
+        <v>星期日</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>worst</v>
       </c>
       <c r="B27" t="str">
-        <v>Sunday</v>
+        <v>/wɜːrst/</v>
       </c>
       <c r="C27" t="str">
-        <v>星期日</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D27" t="str">
-        <v>Sunday(星期日)📢</v>
+        <v>最坏的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>blood</v>
       </c>
       <c r="B28" t="str">
-        <v>would</v>
+        <v>/blʌd/</v>
       </c>
       <c r="C28" t="str">
-        <v>愿意</v>
+        <v>n./vt.</v>
       </c>
       <c r="D28" t="str">
-        <v>would(愿意)📢</v>
+        <v>血</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>ant</v>
       </c>
       <c r="B29" t="str">
-        <v>worst</v>
+        <v>/ænt/</v>
       </c>
       <c r="C29" t="str">
-        <v>最坏的</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>worst(最坏的)📢</v>
+        <v>蚂蚁</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>jaw</v>
       </c>
       <c r="B30" t="str">
-        <v>blood</v>
+        <v>/dʒɔː/</v>
       </c>
       <c r="C30" t="str">
-        <v>血</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>blood(血)📢</v>
+        <v>下巴</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>curse</v>
       </c>
       <c r="B31" t="str">
-        <v>ant</v>
+        <v>/kɜːrs/</v>
       </c>
       <c r="C31" t="str">
-        <v>蚂蚁</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>ant(蚂蚁)📢</v>
+        <v>诅咒</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>awake</v>
       </c>
       <c r="B32" t="str">
-        <v>jaw</v>
+        <v>/əˈweɪk/</v>
       </c>
       <c r="C32" t="str">
-        <v>下巴</v>
+        <v>v./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>jaw(下巴)📢</v>
+        <v>觉醒</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>slogan</v>
       </c>
       <c r="B33" t="str">
-        <v>curse</v>
+        <v>/ˈsloʊɡən/</v>
       </c>
       <c r="C33" t="str">
-        <v>诅咒</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>curse(诅咒)📢</v>
+        <v>标语</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>accessory</v>
       </c>
       <c r="B34" t="str">
-        <v>awake</v>
+        <v>/əkˈsesəri/</v>
       </c>
       <c r="C34" t="str">
-        <v>觉醒</v>
+        <v>n./adj.</v>
       </c>
       <c r="D34" t="str">
-        <v>awake(觉醒)📢</v>
+        <v>附件</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>mess</v>
       </c>
       <c r="B35" t="str">
-        <v>slogan</v>
+        <v>/mes/</v>
       </c>
       <c r="C35" t="str">
-        <v>标语</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>slogan(标语)📢</v>
+        <v>混乱</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>consideration</v>
       </c>
       <c r="B36" t="str">
-        <v>accessory</v>
+        <v>/kənˌsɪdəˈreɪʃn/</v>
       </c>
       <c r="C36" t="str">
-        <v>附件</v>
+        <v>n.</v>
       </c>
       <c r="D36" t="str">
-        <v>accessory(附件)📢</v>
+        <v>关心</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>shelf</v>
       </c>
       <c r="B37" t="str">
-        <v>mess</v>
+        <v>/ʃelf/</v>
       </c>
       <c r="C37" t="str">
-        <v>混乱</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>mess(混乱)📢</v>
+        <v>架子</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>bar</v>
       </c>
       <c r="B38" t="str">
-        <v>consideration</v>
+        <v>/bɑːr/</v>
       </c>
       <c r="C38" t="str">
-        <v>关心</v>
+        <v>n./vt./prep.</v>
       </c>
       <c r="D38" t="str">
-        <v>consideration(关心)📢</v>
+        <v>酒吧</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>pink</v>
       </c>
       <c r="B39" t="str">
-        <v>shelf</v>
+        <v>/pɪŋk/</v>
       </c>
       <c r="C39" t="str">
-        <v>架子</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>shelf(架子)📢</v>
+        <v>粉色</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>cap</v>
       </c>
       <c r="B40" t="str">
-        <v>bar</v>
+        <v>/kæp/</v>
       </c>
       <c r="C40" t="str">
-        <v>酒吧</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>bar(酒吧)📢</v>
+        <v>帽子</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>inhabitant</v>
       </c>
       <c r="B41" t="str">
-        <v>pink</v>
+        <v>/ɪnˈhæbɪtənt/</v>
       </c>
       <c r="C41" t="str">
-        <v>粉色</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>pink(粉色)📢</v>
+        <v>居民</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>proclaim</v>
       </c>
       <c r="B42" t="str">
-        <v>cap</v>
+        <v>/prəˈkleɪm/</v>
       </c>
       <c r="C42" t="str">
-        <v>帽子</v>
+        <v>vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>cap(帽子)📢</v>
+        <v>宣告</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>vague</v>
       </c>
       <c r="B43" t="str">
-        <v>inhabitant</v>
+        <v>/veɪɡ/</v>
       </c>
       <c r="C43" t="str">
-        <v>居民</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>inhabitant(居民)📢</v>
+        <v>模糊</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>outcome</v>
       </c>
       <c r="B44" t="str">
-        <v>castle</v>
+        <v>/ˈaʊtkʌm/</v>
       </c>
       <c r="C44" t="str">
-        <v>城堡</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>castle(城堡)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>village</v>
-      </c>
-      <c r="C45" t="str">
-        <v>村庄</v>
-      </c>
-      <c r="D45" t="str">
-        <v>village(村庄)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>proclaim</v>
-      </c>
-      <c r="C46" t="str">
-        <v>宣告</v>
-      </c>
-      <c r="D46" t="str">
-        <v>proclaim(宣告)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>much</v>
-      </c>
-      <c r="C47" t="str">
-        <v>许多</v>
-      </c>
-      <c r="D47" t="str">
-        <v>much(许多)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>much</v>
-      </c>
-      <c r="C48" t="str">
-        <v>许多</v>
-      </c>
-      <c r="D48" t="str">
-        <v>much(许多)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>employer</v>
-      </c>
-      <c r="C49" t="str">
-        <v>雇主</v>
-      </c>
-      <c r="D49" t="str">
-        <v>employer(雇主)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>vague</v>
-      </c>
-      <c r="C50" t="str">
-        <v>模糊</v>
-      </c>
-      <c r="D50" t="str">
-        <v>vague(模糊)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>outcome</v>
-      </c>
-      <c r="C51" t="str">
         <v>成果</v>
-      </c>
-      <c r="D51" t="str">
-        <v>outcome(成果)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D44"/>
   </ignoredErrors>
 </worksheet>
 </file>